--- a/research/traditional_assets/database/data/india/india_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/india/india_precious_metals.xlsx
@@ -587,8 +587,23 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="G2">
+        <v>-87.24999999999999</v>
+      </c>
+      <c r="H2">
+        <v>-87.24999999999999</v>
+      </c>
+      <c r="I2">
+        <v>-77.25</v>
+      </c>
+      <c r="J2">
+        <v>-77.25</v>
+      </c>
       <c r="K2">
-        <v>-0.369</v>
+        <v>-0.276</v>
+      </c>
+      <c r="L2">
+        <v>-69</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,67 +627,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.011</v>
+        <v>0.212</v>
       </c>
       <c r="V2">
-        <v>0.0003503184713375796</v>
+        <v>0.004930232558139535</v>
       </c>
       <c r="W2">
-        <v>-0.05894568690095846</v>
+        <v>-0.04726027397260275</v>
       </c>
       <c r="X2">
-        <v>0.07614447092401003</v>
+        <v>0.1466590242603055</v>
       </c>
       <c r="Y2">
-        <v>-0.1350901578249685</v>
+        <v>-0.1939192982329083</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.000686224052153028</v>
       </c>
       <c r="AA2">
-        <v>-0.06022745474931925</v>
+        <v>-0.05301080802882141</v>
       </c>
       <c r="AB2">
-        <v>0.07614447092401003</v>
+        <v>0.1458030446282122</v>
       </c>
       <c r="AC2">
-        <v>-0.1363719256733293</v>
+        <v>-0.1988138526570336</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="AG2">
-        <v>-0.011</v>
+        <v>0.204</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.009581721024507094</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.07610684229784119</v>
       </c>
       <c r="AJ2">
-        <v>-0.0003504412373761509</v>
+        <v>0.004721785019905564</v>
       </c>
       <c r="AK2">
-        <v>-0.001887116143420827</v>
+        <v>0.03882755995432052</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-1.355048859934853</v>
+      </c>
+      <c r="AO2">
+        <v>-309</v>
       </c>
       <c r="AP2">
-        <v>0.02972972972972973</v>
+        <v>-0.6644951140065146</v>
       </c>
     </row>
     <row r="3">
@@ -691,8 +709,23 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="G3">
+        <v>-87.24999999999999</v>
+      </c>
+      <c r="H3">
+        <v>-87.24999999999999</v>
+      </c>
+      <c r="I3">
+        <v>-77.25</v>
+      </c>
+      <c r="J3">
+        <v>-77.25</v>
+      </c>
       <c r="K3">
-        <v>-0.369</v>
+        <v>-0.276</v>
+      </c>
+      <c r="L3">
+        <v>-69</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,67 +749,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.011</v>
+        <v>0.212</v>
       </c>
       <c r="V3">
-        <v>0.0003503184713375796</v>
+        <v>0.004930232558139535</v>
       </c>
       <c r="W3">
-        <v>-0.05894568690095846</v>
+        <v>-0.04726027397260275</v>
       </c>
       <c r="X3">
-        <v>0.07614447092401003</v>
+        <v>0.1466590242603055</v>
       </c>
       <c r="Y3">
-        <v>-0.1350901578249685</v>
+        <v>-0.1939192982329083</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.000686224052153028</v>
       </c>
       <c r="AA3">
-        <v>-0.06022745474931925</v>
+        <v>-0.05301080802882141</v>
       </c>
       <c r="AB3">
-        <v>0.07614447092401003</v>
+        <v>0.1458030446282122</v>
       </c>
       <c r="AC3">
-        <v>-0.1363719256733293</v>
+        <v>-0.1988138526570336</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="AG3">
-        <v>-0.011</v>
+        <v>0.204</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.009581721024507094</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.07610684229784119</v>
       </c>
       <c r="AJ3">
-        <v>-0.0003504412373761509</v>
+        <v>0.004721785019905564</v>
       </c>
       <c r="AK3">
-        <v>-0.001887116143420827</v>
+        <v>0.03882755995432052</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-1.355048859934853</v>
+      </c>
+      <c r="AO3">
+        <v>-309</v>
       </c>
       <c r="AP3">
-        <v>0.02972972972972973</v>
+        <v>-0.6644951140065146</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/india/india_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/india/india_precious_metals.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-87.24999999999999</v>
+        <v>-6.674418604651163</v>
       </c>
       <c r="H2">
-        <v>-87.24999999999999</v>
+        <v>-6.674418604651163</v>
       </c>
       <c r="I2">
-        <v>-77.25</v>
+        <v>-17.97674418604651</v>
       </c>
       <c r="J2">
-        <v>-77.25</v>
+        <v>-17.97674418604651</v>
       </c>
       <c r="K2">
-        <v>-0.276</v>
+        <v>-0.252</v>
       </c>
       <c r="L2">
-        <v>-69</v>
+        <v>-5.86046511627907</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,70 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.212</v>
+        <v>2.26</v>
       </c>
       <c r="V2">
-        <v>0.004930232558139535</v>
+        <v>0.009834638816362052</v>
       </c>
       <c r="W2">
-        <v>-0.04726027397260275</v>
+        <v>-0.0499009900990099</v>
       </c>
       <c r="X2">
-        <v>0.1466590242603055</v>
+        <v>0.1224804035485648</v>
       </c>
       <c r="Y2">
-        <v>-0.1939192982329083</v>
+        <v>-0.1723813936475747</v>
       </c>
       <c r="Z2">
-        <v>0.000686224052153028</v>
+        <v>0.008184240578606774</v>
       </c>
       <c r="AA2">
-        <v>-0.05301080802882141</v>
+        <v>-0.1471259992386753</v>
       </c>
       <c r="AB2">
-        <v>0.1458030446282122</v>
+        <v>0.1191939428643279</v>
       </c>
       <c r="AC2">
-        <v>-0.1988138526570336</v>
+        <v>-0.2663199421030031</v>
       </c>
       <c r="AD2">
-        <v>0.416</v>
+        <v>11.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.416</v>
+        <v>11.3</v>
       </c>
       <c r="AG2">
-        <v>0.204</v>
+        <v>9.040000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.009581721024507094</v>
+        <v>0.04686851928660307</v>
       </c>
       <c r="AI2">
-        <v>0.07610684229784119</v>
+        <v>0.2545045045045045</v>
       </c>
       <c r="AJ2">
-        <v>0.004721785019905564</v>
+        <v>0.03784960643108357</v>
       </c>
       <c r="AK2">
-        <v>0.03882755995432052</v>
+        <v>0.2145230185097295</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0.036</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AN2">
-        <v>-1.355048859934853</v>
+        <v>-22.42063492063492</v>
       </c>
       <c r="AO2">
-        <v>-309</v>
+        <v>-21.47222222222222</v>
       </c>
       <c r="AP2">
-        <v>-0.6644951140065146</v>
+        <v>-17.93650793650794</v>
+      </c>
+      <c r="AQ2">
+        <v>-22.73529411764706</v>
       </c>
     </row>
     <row r="3">
@@ -710,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-87.24999999999999</v>
+        <v>-6.674418604651163</v>
       </c>
       <c r="H3">
-        <v>-87.24999999999999</v>
+        <v>-6.674418604651163</v>
       </c>
       <c r="I3">
-        <v>-77.25</v>
+        <v>-17.97674418604651</v>
       </c>
       <c r="J3">
-        <v>-77.25</v>
+        <v>-17.97674418604651</v>
       </c>
       <c r="K3">
-        <v>-0.276</v>
+        <v>-0.252</v>
       </c>
       <c r="L3">
-        <v>-69</v>
+        <v>-5.86046511627907</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,70 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.212</v>
+        <v>2.26</v>
       </c>
       <c r="V3">
-        <v>0.004930232558139535</v>
+        <v>0.009834638816362052</v>
       </c>
       <c r="W3">
-        <v>-0.04726027397260275</v>
+        <v>-0.0499009900990099</v>
       </c>
       <c r="X3">
-        <v>0.1466590242603055</v>
+        <v>0.1224804035485648</v>
       </c>
       <c r="Y3">
-        <v>-0.1939192982329083</v>
+        <v>-0.1723813936475747</v>
       </c>
       <c r="Z3">
-        <v>0.000686224052153028</v>
+        <v>0.008184240578606774</v>
       </c>
       <c r="AA3">
-        <v>-0.05301080802882141</v>
+        <v>-0.1471259992386753</v>
       </c>
       <c r="AB3">
-        <v>0.1458030446282122</v>
+        <v>0.1191939428643279</v>
       </c>
       <c r="AC3">
-        <v>-0.1988138526570336</v>
+        <v>-0.2663199421030031</v>
       </c>
       <c r="AD3">
-        <v>0.416</v>
+        <v>11.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.416</v>
+        <v>11.3</v>
       </c>
       <c r="AG3">
-        <v>0.204</v>
+        <v>9.040000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.009581721024507094</v>
+        <v>0.04686851928660307</v>
       </c>
       <c r="AI3">
-        <v>0.07610684229784119</v>
+        <v>0.2545045045045045</v>
       </c>
       <c r="AJ3">
-        <v>0.004721785019905564</v>
+        <v>0.03784960643108357</v>
       </c>
       <c r="AK3">
-        <v>0.03882755995432052</v>
+        <v>0.2145230185097295</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0.036</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AN3">
-        <v>-1.355048859934853</v>
+        <v>-22.42063492063492</v>
       </c>
       <c r="AO3">
-        <v>-309</v>
+        <v>-21.47222222222222</v>
       </c>
       <c r="AP3">
-        <v>-0.6644951140065146</v>
+        <v>-17.93650793650794</v>
+      </c>
+      <c r="AQ3">
+        <v>-22.73529411764706</v>
       </c>
     </row>
   </sheetData>
